--- a/LTL_qty_updated.xlsx
+++ b/LTL_qty_updated.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C28AEF8-BDEE-41E3-B57F-DED17A927B19}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{617C1542-F887-40B2-9F93-1F0BE3490F72}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="146">
   <si>
     <t>D23_Floor and Wall Tiles</t>
   </si>
@@ -709,12 +709,150 @@
   <si>
     <t>Case_Pallet</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Impero Tuscan Gray Silk 24x48 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>*MOQ of 5*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Impero White Everest Silk 24x48 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>*MOQ of 5*</t>
+    </r>
+  </si>
+  <si>
+    <t>Pietra Limestone White Matte 12x24</t>
+  </si>
+  <si>
+    <t>Pietra Limestone White Stripes 12x24</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Taj Mahal Black Silk 24x48 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>*MOQ of 5*</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Taj Mahal Champagne Silk 12x24 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taj Mahal Gray Silk 12x24 </t>
+  </si>
+  <si>
+    <t>Taj Mahal Ivory Silk 12x24</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Taj Mahal Ivory Silk 24x48 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>*MOQ of 5*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unico Black 12x24 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AKA "Fray Black")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unico Ivory 12x24 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AKA "Fray Ivory")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unico Taupe 12x24 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AKA "Fray Taupe")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unico Tobacco 12x24 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(AKA "Fray Tobacco")</t>
+    </r>
+  </si>
+  <si>
+    <t>Urban Earth Ivory 12x24</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -763,13 +901,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -782,6 +913,20 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -805,7 +950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -843,15 +988,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -864,7 +1000,18 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1194,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -1203,19 +1350,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>131</v>
       </c>
     </row>
@@ -2546,7 +2693,7 @@
       <c r="B83" s="2">
         <v>610010004902</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D83">
@@ -2563,7 +2710,7 @@
       <c r="B84" s="2">
         <v>610010004906</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D84">
@@ -2580,7 +2727,7 @@
       <c r="B85" s="2">
         <v>610010002360</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D85">
@@ -2597,7 +2744,7 @@
       <c r="B86" s="5">
         <v>610010002851</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="14" t="s">
         <v>50</v>
       </c>
       <c r="D86">
@@ -2614,7 +2761,7 @@
       <c r="B87" s="2">
         <v>610010004582</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="14" t="s">
         <v>90</v>
       </c>
       <c r="D87">
@@ -2665,7 +2812,7 @@
       <c r="B90" s="2">
         <v>610010004532</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="3" t="s">
         <v>93</v>
       </c>
       <c r="D90">
@@ -2733,7 +2880,7 @@
       <c r="B94" s="2">
         <v>610010002816</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="14" t="s">
         <v>97</v>
       </c>
       <c r="D94">
@@ -2750,7 +2897,7 @@
       <c r="B95" s="2">
         <v>610010002815</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="14" t="s">
         <v>98</v>
       </c>
       <c r="D95">
@@ -2767,7 +2914,7 @@
       <c r="B96" s="2">
         <v>610010002817</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="14" t="s">
         <v>99</v>
       </c>
       <c r="D96">
@@ -2784,7 +2931,7 @@
       <c r="B97" s="2">
         <v>610110001402</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D97">
@@ -2798,10 +2945,10 @@
       <c r="A98" t="s">
         <v>30</v>
       </c>
-      <c r="B98" s="15">
+      <c r="B98" s="2">
         <v>600010000961</v>
       </c>
-      <c r="C98" s="16" t="s">
+      <c r="C98" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D98">
@@ -2815,10 +2962,10 @@
       <c r="A99" t="s">
         <v>30</v>
       </c>
-      <c r="B99" s="15">
+      <c r="B99" s="2">
         <v>610010004651</v>
       </c>
-      <c r="C99" s="16" t="s">
+      <c r="C99" t="s">
         <v>32</v>
       </c>
       <c r="D99">
@@ -2832,10 +2979,10 @@
       <c r="A100" t="s">
         <v>30</v>
       </c>
-      <c r="B100" s="15">
+      <c r="B100" s="2">
         <v>600010000962</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" t="s">
         <v>100</v>
       </c>
       <c r="D100">
@@ -2849,10 +2996,10 @@
       <c r="A101" t="s">
         <v>30</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B101" s="2">
         <v>610010003151</v>
       </c>
-      <c r="C101" s="7" t="s">
+      <c r="C101" s="3" t="s">
         <v>51</v>
       </c>
       <c r="D101">
@@ -2866,10 +3013,10 @@
       <c r="A102" t="s">
         <v>30</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B102" s="2">
         <v>610010005863</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" t="s">
         <v>101</v>
       </c>
       <c r="D102">
@@ -2883,10 +3030,10 @@
       <c r="A103" t="s">
         <v>30</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B103" s="2">
         <v>610010002001</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" t="s">
         <v>33</v>
       </c>
       <c r="D103">
@@ -2900,10 +3047,10 @@
       <c r="A104" t="s">
         <v>30</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B104" s="2">
         <v>610010004650</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" t="s">
         <v>34</v>
       </c>
       <c r="D104">
@@ -2917,10 +3064,10 @@
       <c r="A105" t="s">
         <v>30</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B105" s="2">
         <v>610010005864</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="14" t="s">
         <v>102</v>
       </c>
       <c r="D105">
@@ -2934,10 +3081,10 @@
       <c r="A106" t="s">
         <v>30</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B106" s="2">
         <v>610010002206</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D106">
@@ -2951,10 +3098,10 @@
       <c r="A107" t="s">
         <v>30</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B107" s="2">
         <v>610010002317</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="14" t="s">
         <v>36</v>
       </c>
       <c r="D107">
@@ -2968,10 +3115,10 @@
       <c r="A108" t="s">
         <v>30</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B108" s="2">
         <v>610010004653</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D108">
@@ -2985,10 +3132,10 @@
       <c r="A109" t="s">
         <v>30</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B109" s="2">
         <v>610010005509</v>
       </c>
-      <c r="C109" s="16" t="s">
+      <c r="C109" s="14" t="s">
         <v>38</v>
       </c>
       <c r="D109">
@@ -3002,10 +3149,10 @@
       <c r="A110" t="s">
         <v>30</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B110" s="2">
         <v>610010005527</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" t="s">
         <v>103</v>
       </c>
       <c r="D110">
@@ -3019,10 +3166,10 @@
       <c r="A111" t="s">
         <v>30</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B111" s="2">
         <v>610010002221</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" t="s">
         <v>104</v>
       </c>
       <c r="D111">
@@ -3036,7 +3183,7 @@
       <c r="A112" t="s">
         <v>30</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B112" s="2">
         <v>610010002315</v>
       </c>
       <c r="C112" s="3" t="s">
@@ -3053,10 +3200,10 @@
       <c r="A113" t="s">
         <v>30</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B113" s="2">
         <v>610010005660</v>
       </c>
-      <c r="C113" s="17" t="s">
+      <c r="C113" t="s">
         <v>106</v>
       </c>
       <c r="D113">
@@ -3070,10 +3217,10 @@
       <c r="A114" t="s">
         <v>30</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B114" s="2">
         <v>610010005788</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="C114" t="s">
         <v>107</v>
       </c>
       <c r="D114">
@@ -3087,10 +3234,10 @@
       <c r="A115" t="s">
         <v>30</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B115" s="2">
         <v>610010005661</v>
       </c>
-      <c r="C115" s="17" t="s">
+      <c r="C115" t="s">
         <v>108</v>
       </c>
       <c r="D115">
@@ -3104,10 +3251,10 @@
       <c r="A116" t="s">
         <v>30</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B116" s="2">
         <v>610010002220</v>
       </c>
-      <c r="C116" s="16" t="s">
+      <c r="C116" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D116">
@@ -3121,10 +3268,10 @@
       <c r="A117" t="s">
         <v>30</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B117" s="2">
         <v>610010004652</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D117">
@@ -3138,10 +3285,10 @@
       <c r="A118" t="s">
         <v>30</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B118" s="2">
         <v>600010000959</v>
       </c>
-      <c r="C118" s="16" t="s">
+      <c r="C118" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D118">
@@ -3155,10 +3302,10 @@
       <c r="A119" t="s">
         <v>30</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B119" s="2">
         <v>610010005866</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="14" t="s">
         <v>109</v>
       </c>
       <c r="D119">
@@ -3172,10 +3319,10 @@
       <c r="A120" t="s">
         <v>30</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B120" s="2">
         <v>610010005865</v>
       </c>
-      <c r="C120" s="3" t="s">
+      <c r="C120" s="14" t="s">
         <v>110</v>
       </c>
       <c r="D120">
@@ -3189,10 +3336,10 @@
       <c r="A121" t="s">
         <v>30</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B121" s="2">
         <v>610010005526</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" t="s">
         <v>111</v>
       </c>
       <c r="D121">
@@ -3206,10 +3353,10 @@
       <c r="A122" t="s">
         <v>30</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B122" s="2">
         <v>610010005571</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" t="s">
         <v>112</v>
       </c>
       <c r="D122">
@@ -3223,7 +3370,7 @@
       <c r="A123" t="s">
         <v>30</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B123" s="2">
         <v>610010005913</v>
       </c>
       <c r="C123" s="3" t="s">
@@ -3240,10 +3387,10 @@
       <c r="A124" t="s">
         <v>30</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B124" s="2">
         <v>610010005912</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" t="s">
         <v>114</v>
       </c>
       <c r="D124">
@@ -3257,10 +3404,10 @@
       <c r="A125" t="s">
         <v>30</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B125" s="2">
         <v>610010005570</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" t="s">
         <v>115</v>
       </c>
       <c r="D125">
@@ -3274,10 +3421,10 @@
       <c r="A126" t="s">
         <v>30</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B126" s="2">
         <v>610010005525</v>
       </c>
-      <c r="C126" s="17" t="s">
+      <c r="C126" t="s">
         <v>116</v>
       </c>
       <c r="D126">
@@ -3287,8 +3434,240 @@
         <v>30</v>
       </c>
     </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>29</v>
+      </c>
+      <c r="B127" s="2">
+        <v>610010006068</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E127">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>29</v>
+      </c>
+      <c r="B128" s="2">
+        <v>610010006069</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E128">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>29</v>
+      </c>
+      <c r="B129" s="2">
+        <v>610010006070</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D129">
+        <v>5</v>
+      </c>
+      <c r="E129">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>29</v>
+      </c>
+      <c r="B130" s="2">
+        <v>610010005867</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D130">
+        <v>5</v>
+      </c>
+      <c r="E130">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>29</v>
+      </c>
+      <c r="B131" s="2">
+        <v>610010006054</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E131">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>29</v>
+      </c>
+      <c r="B132" s="2">
+        <v>610010006097</v>
+      </c>
+      <c r="C132" t="s">
+        <v>137</v>
+      </c>
+      <c r="D132">
+        <v>5</v>
+      </c>
+      <c r="E132">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>29</v>
+      </c>
+      <c r="B133" s="2">
+        <v>610010006098</v>
+      </c>
+      <c r="C133" t="s">
+        <v>138</v>
+      </c>
+      <c r="D133">
+        <v>5</v>
+      </c>
+      <c r="E133">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>29</v>
+      </c>
+      <c r="B134" s="2">
+        <v>610010006073</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D134">
+        <v>5</v>
+      </c>
+      <c r="E134">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B135" s="2">
+        <v>610010005960</v>
+      </c>
+      <c r="C135" t="s">
+        <v>140</v>
+      </c>
+      <c r="E135">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>29</v>
+      </c>
+      <c r="B136" s="2">
+        <v>610010004563</v>
+      </c>
+      <c r="C136" t="s">
+        <v>141</v>
+      </c>
+      <c r="D136">
+        <v>5</v>
+      </c>
+      <c r="E136">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B137" s="2">
+        <v>610010004560</v>
+      </c>
+      <c r="C137" t="s">
+        <v>142</v>
+      </c>
+      <c r="D137">
+        <v>5</v>
+      </c>
+      <c r="E137">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" s="2">
+        <v>610010004561</v>
+      </c>
+      <c r="C138" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D138">
+        <v>5</v>
+      </c>
+      <c r="E138">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>29</v>
+      </c>
+      <c r="B139" s="2">
+        <v>610010004562</v>
+      </c>
+      <c r="C139" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D139">
+        <v>5</v>
+      </c>
+      <c r="E139">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>29</v>
+      </c>
+      <c r="B140" s="2">
+        <v>610010006072</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D140">
+        <v>5</v>
+      </c>
+      <c r="E140">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C141" s="14"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E126" xr:uid="{F30446A3-A986-4686-A765-4C12AB9F4FB1}"/>
+  <conditionalFormatting sqref="B2:B140">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C8" r:id="rId1" xr:uid="{89506ED6-C4FD-47B8-9FD6-878DCA92E9AA}"/>
     <hyperlink ref="C18" r:id="rId2" xr:uid="{7B1ECE4D-B039-4F94-838C-A478D53267E0}"/>

--- a/LTL_qty_updated.xlsx
+++ b/LTL_qty_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acusa-my.sharepoint.com/personal/g_ghedini_atlasconcordeusa_com/Documents/Desktop/AI - Automations/BOL creation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{617C1542-F887-40B2-9F93-1F0BE3490F72}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{41BA2822-1FC3-424A-BF5C-A2447EBC91C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5E322A6-2B2F-4593-A253-7739BCE3D4DC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{B388D9E8-F042-4987-BDB7-8E3EC1CFA04A}"/>
   </bookViews>
@@ -2461,8 +2461,8 @@
       <c r="D69">
         <v>16</v>
       </c>
-      <c r="E69" t="e">
-        <v>#N/A</v>
+      <c r="E69">
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -2478,8 +2478,8 @@
       <c r="D70">
         <v>16</v>
       </c>
-      <c r="E70" t="e">
-        <v>#N/A</v>
+      <c r="E70">
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -2495,8 +2495,8 @@
       <c r="D71">
         <v>16</v>
       </c>
-      <c r="E71" t="e">
-        <v>#N/A</v>
+      <c r="E71">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -2512,8 +2512,8 @@
       <c r="D72">
         <v>16</v>
       </c>
-      <c r="E72" t="e">
-        <v>#N/A</v>
+      <c r="E72">
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -2529,8 +2529,8 @@
       <c r="D73">
         <v>16</v>
       </c>
-      <c r="E73" t="e">
-        <v>#N/A</v>
+      <c r="E73">
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
